--- a/artfynd/S 1083-2025 artfynd.xlsx
+++ b/artfynd/S 1083-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85257</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96996983</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997089</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/585526</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103267009</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997052</t>
         </is>
       </c>
     </row>
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103267018</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1174003</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997711</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997712</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997716</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1277008</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95333700</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95333702</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95333704</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997609</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997618</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2494,6 +2584,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997619</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2595,6 +2690,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997620</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2696,6 +2796,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997621</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2797,6 +2902,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997622</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2898,6 +3008,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997683</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2999,6 +3114,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997684</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3100,6 +3220,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997685</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3201,6 +3326,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997686</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,6 +3432,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997687</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3401,6 +3536,11 @@
       <c r="AY28" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997689</t>
         </is>
       </c>
     </row>
@@ -3504,6 +3644,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103267011</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3605,6 +3750,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997132</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3706,6 +3856,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997138</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3820,6 +3975,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045868</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3922,6 +4082,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1757020</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4024,6 +4189,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1757021</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4125,6 +4295,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103267019</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4226,6 +4401,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997276</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4340,6 +4520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045408</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4441,8 +4626,52 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96997173</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>